--- a/ig/travaux-tru/StructureDefinition-esms-consent.xlsx
+++ b/ig/travaux-tru/StructureDefinition-esms-consent.xlsx
@@ -24,7 +24,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/fhir/sdo-esms/esms-consent</t>
+    <t>https://interop.esante.gouv.fr/ig/fhir/sdo/StructureDefinition/esms-consent</t>
   </si>
   <si>
     <t>Version</t>
@@ -1286,7 +1286,7 @@
     <t>Consent.provision.data.reference</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://esante.gouv.fr/fhir/ms/StructureDefinition/sdo-task)
+    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/fhir/sdo/sdo-task)
 </t>
   </si>
   <si>
